--- a/ri_plus_4438/urdf/initial.xlsx
+++ b/ri_plus_4438/urdf/initial.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="594">
   <si>
     <t>base_link 的质量属性</t>
   </si>
@@ -242,7 +242,7 @@
     <t>质量 = 0.31383978 千克</t>
   </si>
   <si>
-    <t>质量 = 0.07421078 千克</t>
+    <t>质量 = 0.06406078 千克</t>
   </si>
   <si>
     <t>质量 = 0.06068055 千克</t>
@@ -281,7 +281,7 @@
     <t>体积 = 0.00012164 立方米</t>
   </si>
   <si>
-    <t>体积 = 0.00005576 立方米</t>
+    <t>体积 = 0.00004414 立方米</t>
   </si>
   <si>
     <t>体积 = 0.00005567 立方米</t>
@@ -323,10 +323,7 @@
     <t>表面积 = 0.07342474 平方米</t>
   </si>
   <si>
-    <t>表面积 = 0.04271919 平方米</t>
-  </si>
-  <si>
-    <t>表面积 = 0.04271918 平方米</t>
+    <t>表面积 = 0.03657147 平方米</t>
   </si>
   <si>
     <t>表面积 = 0.01633342 平方米</t>
@@ -380,7 +377,7 @@
     <t>X = 0.04099855</t>
   </si>
   <si>
-    <t>X = 0.01603516</t>
+    <t>X = 0.01860227</t>
   </si>
   <si>
     <t>Y = 0.00204115</t>
@@ -431,10 +428,10 @@
     <t>Y = -0.00008900</t>
   </si>
   <si>
-    <t>Y = 0.05927323</t>
-  </si>
-  <si>
-    <t>Y = -0.05927323</t>
+    <t>Y = 0.05889209</t>
+  </si>
+  <si>
+    <t>Y = -0.05889209</t>
   </si>
   <si>
     <t>Z = -0.00063500</t>
@@ -485,10 +482,10 @@
     <t>Z = 0.01150782</t>
   </si>
   <si>
-    <t>Z = -0.00696726</t>
-  </si>
-  <si>
-    <t>Z = -0.00465155</t>
+    <t>Z = -0.00134131</t>
+  </si>
+  <si>
+    <t>Z = 0.00134131</t>
   </si>
   <si>
     <t>Z = -0.05890115</t>
@@ -593,16 +590,13 @@
     <t>Px = 0.00016428</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ix = ( 0.70373907, -0.11569911,  0.70097435)   </t>
-  </si>
-  <si>
-    <t>Px = 0.00002095</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ix = ( 0.65236050,  0.11266996,  0.74948733)   </t>
-  </si>
-  <si>
-    <t>Px = 0.00002473</t>
+    <t xml:space="preserve"> Ix = ( 0.97503307, -0.18812587,  0.11797953)   </t>
+  </si>
+  <si>
+    <t>Px = 0.00001197</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ix = ( 0.97503307,  0.18812587, -0.11797953)   </t>
   </si>
   <si>
     <t xml:space="preserve"> Iy = ( 0.06976381,  0.99751104,  0.01023372)   </t>
@@ -704,16 +698,13 @@
     <t>Py = 0.00032802</t>
   </si>
   <si>
-    <t xml:space="preserve"> Iy = ( 0.68007496, -0.17574944, -0.71176553)   </t>
-  </si>
-  <si>
-    <t>Py = 0.00003994</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Iy = ( 0.73364527,  0.15433988, -0.66177324)   </t>
-  </si>
-  <si>
-    <t>Py = 0.00003819</t>
+    <t xml:space="preserve"> Iy = ( 0.10212233, -0.09189702, -0.99051803)   </t>
+  </si>
+  <si>
+    <t>Py = 0.00002591</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Iy = (-0.10212233, -0.09189702, -0.99051803)   </t>
   </si>
   <si>
     <t xml:space="preserve"> Iz = ( 0.00381364, -0.01052533,  0.99993733)   </t>
@@ -815,16 +806,13 @@
     <t>Pz = 0.00035441</t>
   </si>
   <si>
-    <t xml:space="preserve"> Iz = ( 0.20554649,  0.97761232, -0.04499768)   </t>
-  </si>
-  <si>
-    <t>Pz = 0.00004976</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Iz = (-0.19023775,  0.98157256,  0.01802545)   </t>
-  </si>
-  <si>
-    <t>Pz = 0.00005173</t>
+    <t xml:space="preserve"> Iz = ( 0.19718403,  0.97783618, -0.07039078)   </t>
+  </si>
+  <si>
+    <t>Pz = 0.00002839</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Iz = (-0.19718403,  0.97783618, -0.07039078)   </t>
   </si>
   <si>
     <t xml:space="preserve"> Iz = ( 0.00025581,  0.99999996, -0.00007035)   </t>
@@ -968,22 +956,19 @@
     <t>Lxz = -0.00008101</t>
   </si>
   <si>
-    <t>Lxx = 0.00003095</t>
-  </si>
-  <si>
-    <t>Lxy = 0.00000352</t>
-  </si>
-  <si>
-    <t>Lxz = -0.00000946</t>
-  </si>
-  <si>
-    <t>Lxx = 0.00003295</t>
-  </si>
-  <si>
-    <t>Lxy = -0.00000352</t>
-  </si>
-  <si>
-    <t>Lxz = -0.00000662</t>
+    <t>Lxx = 0.00001275</t>
+  </si>
+  <si>
+    <t>Lxy = 0.00000303</t>
+  </si>
+  <si>
+    <t>Lxz = -0.00000164</t>
+  </si>
+  <si>
+    <t>Lxy = -0.00000303</t>
+  </si>
+  <si>
+    <t>Lxz = 0.00000164</t>
   </si>
   <si>
     <t>Lyx = 0.00048912</t>
@@ -1124,22 +1109,16 @@
     <t>Lyz = 0.00000289</t>
   </si>
   <si>
-    <t>Lyx = 0.00000352</t>
-  </si>
-  <si>
-    <t>Lyy = 0.00004907</t>
-  </si>
-  <si>
-    <t>Lyz = 0.00000111</t>
-  </si>
-  <si>
-    <t>Lyx = -0.00000352</t>
-  </si>
-  <si>
-    <t>Lyy = 0.00005106</t>
-  </si>
-  <si>
-    <t>Lyz = -0.00000090</t>
+    <t>Lyx = 0.00000303</t>
+  </si>
+  <si>
+    <t>Lyy = 0.00002778</t>
+  </si>
+  <si>
+    <t>Lyz = 0.00000014</t>
+  </si>
+  <si>
+    <t>Lyx = -0.00000303</t>
   </si>
   <si>
     <t>Lzx = 0.00004378</t>
@@ -1280,19 +1259,16 @@
     <t>Lzz = 0.00020970</t>
   </si>
   <si>
-    <t>Lzx = -0.00000946</t>
-  </si>
-  <si>
-    <t>Lzy = 0.00000111</t>
-  </si>
-  <si>
-    <t>Lzz = 0.00003063</t>
-  </si>
-  <si>
-    <t>Lzx = -0.00000662</t>
-  </si>
-  <si>
-    <t>Lzy = -0.00000090</t>
+    <t>Lzx = -0.00000164</t>
+  </si>
+  <si>
+    <t>Lzy = 0.00000014</t>
+  </si>
+  <si>
+    <t>Lzz = 0.00002573</t>
+  </si>
+  <si>
+    <t>Lzx = 0.00000164</t>
   </si>
   <si>
     <t>Lzx = 0.00001460</t>
@@ -1439,19 +1415,19 @@
     <t>Ixz = -0.00022908</t>
   </si>
   <si>
-    <t>Ixx = 0.00029528</t>
-  </si>
-  <si>
-    <t>Ixy = -0.00006702</t>
-  </si>
-  <si>
-    <t>Ixz = -0.00000117</t>
-  </si>
-  <si>
-    <t>Ixy = 0.00006702</t>
-  </si>
-  <si>
-    <t>Ixz = -0.00000109</t>
+    <t>Ixx = 0.00023505</t>
+  </si>
+  <si>
+    <t>Ixy = -0.00006715</t>
+  </si>
+  <si>
+    <t>Ixz = -0.00000004</t>
+  </si>
+  <si>
+    <t>Ixy = 0.00006715</t>
+  </si>
+  <si>
+    <t>Ixz = 0.00000004</t>
   </si>
   <si>
     <t>Iyx = 0.00050600</t>
@@ -1580,19 +1556,16 @@
     <t>Iyz = 0.00000322</t>
   </si>
   <si>
-    <t>Iyx = -0.00006702</t>
-  </si>
-  <si>
-    <t>Iyy = 0.00007175</t>
-  </si>
-  <si>
-    <t>Iyz = 0.00003176</t>
-  </si>
-  <si>
-    <t>Iyx = 0.00006702</t>
-  </si>
-  <si>
-    <t>Iyz = -0.00002136</t>
+    <t>Iyx = -0.00006715</t>
+  </si>
+  <si>
+    <t>Iyy = 0.00005007</t>
+  </si>
+  <si>
+    <t>Iyz = 0.00000520</t>
+  </si>
+  <si>
+    <t>Iyx = 0.00006715</t>
   </si>
   <si>
     <t>Izx = 0.00003853</t>
@@ -1727,19 +1700,16 @@
     <t>Izz = 0.00073723</t>
   </si>
   <si>
-    <t>Izx = -0.00000117</t>
-  </si>
-  <si>
-    <t>Izy = 0.00003176</t>
-  </si>
-  <si>
-    <t>Izz = 0.00031044</t>
-  </si>
-  <si>
-    <t>Izx = -0.00000109</t>
-  </si>
-  <si>
-    <t>Izy = -0.00002136</t>
+    <t>Izx = -0.00000004</t>
+  </si>
+  <si>
+    <t>Izy = 0.00000520</t>
+  </si>
+  <si>
+    <t>Izz = 0.00027007</t>
+  </si>
+  <si>
+    <t>Izx = 0.00000004</t>
   </si>
   <si>
     <t>Izx = 0.00005052</t>
@@ -1809,9 +1779,6 @@
   </si>
   <si>
     <t>Gripper-Camera_Connect_A-&lt;1&gt;&lt;默认&gt;</t>
-  </si>
-  <si>
-    <t>gripper_connect_L&lt;默认&gt;</t>
   </si>
   <si>
     <t>OLED背板&lt;1&gt;&lt;默认&gt;@HT-Pi-03C-BODY-后盖总成&lt;1&gt;&lt;默认&gt;@base_down&lt;1&gt;&lt;默认&gt;</t>
@@ -3254,10 +3221,10 @@
         <v>32</v>
       </c>
       <c r="EO2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="EU2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:152">
@@ -3581,2939 +3548,2939 @@
         <v>98</v>
       </c>
       <c r="EU9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:152">
       <c r="S10" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y10" t="s">
         <v>100</v>
       </c>
-      <c r="Y10" t="s">
-        <v>101</v>
-      </c>
       <c r="AQ10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW10" t="s">
         <v>100</v>
       </c>
-      <c r="AW10" t="s">
-        <v>101</v>
-      </c>
       <c r="BO10" t="s">
+        <v>99</v>
+      </c>
+      <c r="BU10" t="s">
         <v>100</v>
       </c>
-      <c r="BU10" t="s">
-        <v>101</v>
-      </c>
       <c r="CM10" t="s">
+        <v>99</v>
+      </c>
+      <c r="CS10" t="s">
         <v>100</v>
-      </c>
-      <c r="CS10" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:152">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AE11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BC11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BI11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="CA11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="CG11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="CY11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="DE11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="DK11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="DQ11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="DW11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="EC11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="EI11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="EO11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="EU11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:152">
       <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" t="s">
         <v>103</v>
       </c>
-      <c r="H12" t="s">
+      <c r="N12" t="s">
         <v>104</v>
       </c>
-      <c r="N12" t="s">
+      <c r="S12" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL12" t="s">
         <v>105</v>
       </c>
-      <c r="S12" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>102</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL12" t="s">
+      <c r="AQ12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>101</v>
+      </c>
+      <c r="BD12" t="s">
         <v>106</v>
       </c>
-      <c r="AQ12" t="s">
-        <v>102</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD12" t="s">
+      <c r="BJ12" t="s">
         <v>107</v>
       </c>
-      <c r="BJ12" t="s">
+      <c r="BO12" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>101</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>106</v>
+      </c>
+      <c r="CH12" t="s">
         <v>108</v>
       </c>
-      <c r="BO12" t="s">
-        <v>102</v>
-      </c>
-      <c r="BU12" t="s">
-        <v>102</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>107</v>
-      </c>
-      <c r="CH12" t="s">
+      <c r="CM12" t="s">
+        <v>101</v>
+      </c>
+      <c r="CS12" t="s">
+        <v>101</v>
+      </c>
+      <c r="CZ12" t="s">
         <v>109</v>
       </c>
-      <c r="CM12" t="s">
-        <v>102</v>
-      </c>
-      <c r="CS12" t="s">
-        <v>102</v>
-      </c>
-      <c r="CZ12" t="s">
+      <c r="DF12" t="s">
         <v>110</v>
       </c>
-      <c r="DF12" t="s">
+      <c r="DL12" t="s">
         <v>111</v>
       </c>
-      <c r="DL12" t="s">
+      <c r="DR12" t="s">
         <v>112</v>
       </c>
-      <c r="DR12" t="s">
+      <c r="DX12" t="s">
         <v>113</v>
       </c>
-      <c r="DX12" t="s">
+      <c r="ED12" t="s">
         <v>114</v>
       </c>
-      <c r="ED12" t="s">
+      <c r="EJ12" t="s">
         <v>115</v>
       </c>
-      <c r="EJ12" t="s">
+      <c r="EP12" t="s">
         <v>116</v>
       </c>
-      <c r="EP12" t="s">
-        <v>117</v>
-      </c>
       <c r="EV12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:152">
       <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" t="s">
         <v>118</v>
       </c>
-      <c r="H13" t="s">
+      <c r="N13" t="s">
         <v>119</v>
       </c>
-      <c r="N13" t="s">
+      <c r="T13" t="s">
         <v>120</v>
       </c>
-      <c r="T13" t="s">
+      <c r="Z13" t="s">
         <v>121</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AF13" t="s">
         <v>122</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AL13" t="s">
         <v>123</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AR13" t="s">
         <v>124</v>
       </c>
-      <c r="AR13" t="s">
+      <c r="AX13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>119</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV13" t="s">
+        <v>121</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>122</v>
+      </c>
+      <c r="CH13" t="s">
         <v>125</v>
       </c>
-      <c r="AX13" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>119</v>
-      </c>
-      <c r="BJ13" t="s">
+      <c r="CN13" t="s">
         <v>120</v>
       </c>
-      <c r="BP13" t="s">
+      <c r="CT13" t="s">
         <v>121</v>
       </c>
-      <c r="BV13" t="s">
-        <v>122</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>123</v>
-      </c>
-      <c r="CH13" t="s">
+      <c r="CZ13" t="s">
         <v>126</v>
       </c>
-      <c r="CN13" t="s">
-        <v>121</v>
-      </c>
-      <c r="CT13" t="s">
-        <v>122</v>
-      </c>
-      <c r="CZ13" t="s">
+      <c r="DF13" t="s">
         <v>127</v>
       </c>
-      <c r="DF13" t="s">
+      <c r="DL13" t="s">
         <v>128</v>
       </c>
-      <c r="DL13" t="s">
+      <c r="DR13" t="s">
         <v>129</v>
       </c>
-      <c r="DR13" t="s">
+      <c r="DX13" t="s">
         <v>130</v>
       </c>
-      <c r="DX13" t="s">
+      <c r="ED13" t="s">
         <v>131</v>
       </c>
-      <c r="ED13" t="s">
+      <c r="EJ13" t="s">
         <v>132</v>
       </c>
-      <c r="EJ13" t="s">
+      <c r="EP13" t="s">
         <v>133</v>
       </c>
-      <c r="EP13" t="s">
+      <c r="EV13" t="s">
         <v>134</v>
-      </c>
-      <c r="EV13" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:152">
       <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" t="s">
         <v>136</v>
       </c>
-      <c r="H14" t="s">
+      <c r="N14" t="s">
         <v>137</v>
       </c>
-      <c r="N14" t="s">
+      <c r="T14" t="s">
         <v>138</v>
       </c>
-      <c r="T14" t="s">
+      <c r="Z14" t="s">
         <v>139</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AF14" t="s">
         <v>140</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AL14" t="s">
         <v>141</v>
       </c>
-      <c r="AL14" t="s">
+      <c r="AR14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>139</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>140</v>
+      </c>
+      <c r="BJ14" t="s">
         <v>142</v>
       </c>
-      <c r="AR14" t="s">
+      <c r="BP14" t="s">
+        <v>138</v>
+      </c>
+      <c r="BV14" t="s">
         <v>139</v>
       </c>
-      <c r="AX14" t="s">
-        <v>140</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>141</v>
-      </c>
-      <c r="BJ14" t="s">
+      <c r="CB14" t="s">
+        <v>136</v>
+      </c>
+      <c r="CH14" t="s">
         <v>143</v>
       </c>
-      <c r="BP14" t="s">
+      <c r="CN14" t="s">
+        <v>138</v>
+      </c>
+      <c r="CT14" t="s">
         <v>139</v>
       </c>
-      <c r="BV14" t="s">
-        <v>140</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>137</v>
-      </c>
-      <c r="CH14" t="s">
+      <c r="CZ14" t="s">
         <v>144</v>
       </c>
-      <c r="CN14" t="s">
-        <v>139</v>
-      </c>
-      <c r="CT14" t="s">
-        <v>140</v>
-      </c>
-      <c r="CZ14" t="s">
+      <c r="DF14" t="s">
         <v>145</v>
       </c>
-      <c r="DF14" t="s">
+      <c r="DL14" t="s">
         <v>146</v>
       </c>
-      <c r="DL14" t="s">
+      <c r="DR14" t="s">
         <v>147</v>
       </c>
-      <c r="DR14" t="s">
+      <c r="DX14" t="s">
         <v>148</v>
       </c>
-      <c r="DX14" t="s">
+      <c r="ED14" t="s">
         <v>149</v>
       </c>
-      <c r="ED14" t="s">
+      <c r="EJ14" t="s">
         <v>150</v>
       </c>
-      <c r="EJ14" t="s">
+      <c r="EP14" t="s">
         <v>151</v>
       </c>
-      <c r="EP14" t="s">
+      <c r="EV14" t="s">
         <v>152</v>
-      </c>
-      <c r="EV14" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:152">
       <c r="T15" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z15" t="s">
         <v>154</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AR15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AX15" t="s">
         <v>155</v>
       </c>
-      <c r="AR15" t="s">
+      <c r="BP15" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV15" t="s">
         <v>154</v>
       </c>
-      <c r="AX15" t="s">
-        <v>156</v>
-      </c>
-      <c r="BP15" t="s">
+      <c r="CN15" t="s">
+        <v>153</v>
+      </c>
+      <c r="CT15" t="s">
         <v>154</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>155</v>
-      </c>
-      <c r="CN15" t="s">
-        <v>154</v>
-      </c>
-      <c r="CT15" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:152">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AE16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AK16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BC16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BI16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="CA16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="CG16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="CY16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="DE16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="DK16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="DQ16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="DW16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="EC16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="EI16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="EO16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="EU16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:154">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S17" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE17" t="s">
         <v>157</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AK17" t="s">
         <v>157</v>
       </c>
-      <c r="AE17" t="s">
-        <v>158</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>158</v>
-      </c>
       <c r="AQ17" t="s">
+        <v>156</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>156</v>
+      </c>
+      <c r="BC17" t="s">
         <v>157</v>
       </c>
-      <c r="AW17" t="s">
+      <c r="BI17" t="s">
         <v>157</v>
       </c>
-      <c r="BC17" t="s">
-        <v>158</v>
-      </c>
-      <c r="BI17" t="s">
-        <v>158</v>
-      </c>
       <c r="BO17" t="s">
+        <v>156</v>
+      </c>
+      <c r="BU17" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA17" t="s">
         <v>157</v>
       </c>
-      <c r="BU17" t="s">
+      <c r="CG17" t="s">
         <v>157</v>
       </c>
-      <c r="CA17" t="s">
-        <v>158</v>
-      </c>
-      <c r="CG17" t="s">
-        <v>158</v>
-      </c>
       <c r="CM17" t="s">
+        <v>156</v>
+      </c>
+      <c r="CS17" t="s">
+        <v>156</v>
+      </c>
+      <c r="CY17" t="s">
         <v>157</v>
       </c>
-      <c r="CS17" t="s">
+      <c r="DE17" t="s">
         <v>157</v>
       </c>
-      <c r="CY17" t="s">
-        <v>158</v>
-      </c>
-      <c r="DE17" t="s">
-        <v>158</v>
-      </c>
       <c r="DK17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="DQ17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="DW17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="EC17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="EI17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="EO17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="EU17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:154">
       <c r="B18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" t="s">
         <v>159</v>
       </c>
-      <c r="C18" t="s">
+      <c r="H18" t="s">
         <v>160</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>161</v>
       </c>
-      <c r="I18" t="s">
+      <c r="N18" t="s">
         <v>162</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>163</v>
       </c>
-      <c r="O18" t="s">
+      <c r="S18" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF18" t="s">
         <v>164</v>
       </c>
-      <c r="S18" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>158</v>
-      </c>
-      <c r="AF18" t="s">
+      <c r="AG18" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL18" t="s">
         <v>165</v>
       </c>
-      <c r="AG18" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL18" t="s">
+      <c r="AM18" t="s">
         <v>166</v>
       </c>
-      <c r="AM18" t="s">
+      <c r="AQ18" t="s">
+        <v>157</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>157</v>
+      </c>
+      <c r="BD18" t="s">
         <v>167</v>
       </c>
-      <c r="AQ18" t="s">
-        <v>158</v>
-      </c>
-      <c r="AW18" t="s">
-        <v>158</v>
-      </c>
-      <c r="BD18" t="s">
+      <c r="BE18" t="s">
+        <v>161</v>
+      </c>
+      <c r="BJ18" t="s">
         <v>168</v>
       </c>
-      <c r="BE18" t="s">
-        <v>162</v>
-      </c>
-      <c r="BJ18" t="s">
+      <c r="BK18" t="s">
         <v>169</v>
       </c>
-      <c r="BK18" t="s">
+      <c r="BO18" t="s">
+        <v>157</v>
+      </c>
+      <c r="BU18" t="s">
+        <v>157</v>
+      </c>
+      <c r="CB18" t="s">
         <v>170</v>
       </c>
-      <c r="BO18" t="s">
-        <v>158</v>
-      </c>
-      <c r="BU18" t="s">
-        <v>158</v>
-      </c>
-      <c r="CB18" t="s">
+      <c r="CC18" t="s">
+        <v>161</v>
+      </c>
+      <c r="CH18" t="s">
         <v>171</v>
       </c>
-      <c r="CC18" t="s">
-        <v>162</v>
-      </c>
-      <c r="CH18" t="s">
+      <c r="CI18" t="s">
         <v>172</v>
       </c>
-      <c r="CI18" t="s">
+      <c r="CM18" t="s">
+        <v>157</v>
+      </c>
+      <c r="CS18" t="s">
+        <v>157</v>
+      </c>
+      <c r="CZ18" t="s">
         <v>173</v>
       </c>
-      <c r="CM18" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS18" t="s">
-        <v>158</v>
-      </c>
-      <c r="CZ18" t="s">
+      <c r="DA18" t="s">
         <v>174</v>
       </c>
-      <c r="DA18" t="s">
+      <c r="DF18" t="s">
         <v>175</v>
       </c>
-      <c r="DF18" t="s">
+      <c r="DG18" t="s">
         <v>176</v>
       </c>
-      <c r="DG18" t="s">
+      <c r="DL18" t="s">
         <v>177</v>
       </c>
-      <c r="DL18" t="s">
+      <c r="DM18" t="s">
         <v>178</v>
       </c>
-      <c r="DM18" t="s">
+      <c r="DR18" t="s">
         <v>179</v>
       </c>
-      <c r="DR18" t="s">
+      <c r="DS18" t="s">
         <v>180</v>
       </c>
-      <c r="DS18" t="s">
+      <c r="DX18" t="s">
         <v>181</v>
       </c>
-      <c r="DX18" t="s">
+      <c r="DY18" t="s">
         <v>182</v>
       </c>
-      <c r="DY18" t="s">
+      <c r="ED18" t="s">
         <v>183</v>
       </c>
-      <c r="ED18" t="s">
+      <c r="EE18" t="s">
         <v>184</v>
       </c>
-      <c r="EE18" t="s">
+      <c r="EJ18" t="s">
         <v>185</v>
       </c>
-      <c r="EJ18" t="s">
+      <c r="EK18" t="s">
         <v>186</v>
       </c>
-      <c r="EK18" t="s">
+      <c r="EP18" t="s">
         <v>187</v>
       </c>
-      <c r="EP18" t="s">
+      <c r="EQ18" t="s">
         <v>188</v>
       </c>
-      <c r="EQ18" t="s">
+      <c r="EV18" t="s">
         <v>189</v>
       </c>
-      <c r="EV18" t="s">
-        <v>190</v>
-      </c>
       <c r="EW18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:154">
       <c r="B19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" t="s">
+        <v>191</v>
+      </c>
+      <c r="H19" t="s">
         <v>192</v>
       </c>
-      <c r="C19" t="s">
+      <c r="I19" t="s">
         <v>193</v>
       </c>
-      <c r="H19" t="s">
+      <c r="N19" t="s">
         <v>194</v>
       </c>
-      <c r="I19" t="s">
+      <c r="O19" t="s">
         <v>195</v>
       </c>
-      <c r="N19" t="s">
+      <c r="T19" t="s">
         <v>196</v>
       </c>
-      <c r="O19" t="s">
+      <c r="U19" t="s">
         <v>197</v>
       </c>
-      <c r="T19" t="s">
+      <c r="Z19" t="s">
         <v>198</v>
       </c>
-      <c r="U19" t="s">
+      <c r="AA19" t="s">
         <v>199</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AF19" t="s">
         <v>200</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AG19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL19" t="s">
         <v>201</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AM19" t="s">
         <v>202</v>
       </c>
-      <c r="AG19" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL19" t="s">
+      <c r="AR19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>199</v>
+      </c>
+      <c r="BD19" t="s">
         <v>203</v>
       </c>
-      <c r="AM19" t="s">
+      <c r="BE19" t="s">
+        <v>193</v>
+      </c>
+      <c r="BJ19" t="s">
         <v>204</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="BK19" t="s">
+        <v>205</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>196</v>
+      </c>
+      <c r="BQ19" t="s">
+        <v>197</v>
+      </c>
+      <c r="BV19" t="s">
         <v>198</v>
       </c>
-      <c r="AS19" t="s">
+      <c r="BW19" t="s">
         <v>199</v>
       </c>
-      <c r="AX19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>205</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>195</v>
-      </c>
-      <c r="BJ19" t="s">
+      <c r="CB19" t="s">
         <v>206</v>
       </c>
-      <c r="BK19" t="s">
+      <c r="CC19" t="s">
+        <v>193</v>
+      </c>
+      <c r="CH19" t="s">
         <v>207</v>
       </c>
-      <c r="BP19" t="s">
+      <c r="CI19" t="s">
+        <v>208</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>196</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>197</v>
+      </c>
+      <c r="CT19" t="s">
         <v>198</v>
       </c>
-      <c r="BQ19" t="s">
+      <c r="CU19" t="s">
         <v>199</v>
       </c>
-      <c r="BV19" t="s">
-        <v>200</v>
-      </c>
-      <c r="BW19" t="s">
-        <v>201</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>208</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>195</v>
-      </c>
-      <c r="CH19" t="s">
+      <c r="CZ19" t="s">
         <v>209</v>
       </c>
-      <c r="CI19" t="s">
+      <c r="DA19" t="s">
         <v>210</v>
       </c>
-      <c r="CN19" t="s">
-        <v>198</v>
-      </c>
-      <c r="CO19" t="s">
-        <v>199</v>
-      </c>
-      <c r="CT19" t="s">
-        <v>200</v>
-      </c>
-      <c r="CU19" t="s">
-        <v>201</v>
-      </c>
-      <c r="CZ19" t="s">
+      <c r="DF19" t="s">
         <v>211</v>
       </c>
-      <c r="DA19" t="s">
+      <c r="DG19" t="s">
         <v>212</v>
       </c>
-      <c r="DF19" t="s">
+      <c r="DL19" t="s">
         <v>213</v>
       </c>
-      <c r="DG19" t="s">
+      <c r="DM19" t="s">
         <v>214</v>
       </c>
-      <c r="DL19" t="s">
+      <c r="DR19" t="s">
         <v>215</v>
       </c>
-      <c r="DM19" t="s">
+      <c r="DS19" t="s">
         <v>216</v>
       </c>
-      <c r="DR19" t="s">
+      <c r="DX19" t="s">
         <v>217</v>
       </c>
-      <c r="DS19" t="s">
+      <c r="DY19" t="s">
         <v>218</v>
       </c>
-      <c r="DX19" t="s">
+      <c r="ED19" t="s">
         <v>219</v>
       </c>
-      <c r="DY19" t="s">
+      <c r="EE19" t="s">
         <v>220</v>
       </c>
-      <c r="ED19" t="s">
+      <c r="EJ19" t="s">
         <v>221</v>
       </c>
-      <c r="EE19" t="s">
+      <c r="EK19" t="s">
         <v>222</v>
       </c>
-      <c r="EJ19" t="s">
+      <c r="EP19" t="s">
         <v>223</v>
       </c>
-      <c r="EK19" t="s">
+      <c r="EQ19" t="s">
         <v>224</v>
       </c>
-      <c r="EP19" t="s">
+      <c r="EV19" t="s">
         <v>225</v>
       </c>
-      <c r="EQ19" t="s">
-        <v>226</v>
-      </c>
-      <c r="EV19" t="s">
-        <v>227</v>
-      </c>
       <c r="EW19" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:154">
       <c r="B20" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" t="s">
         <v>229</v>
       </c>
-      <c r="C20" t="s">
+      <c r="N20" t="s">
         <v>230</v>
       </c>
-      <c r="H20" t="s">
+      <c r="O20" t="s">
         <v>231</v>
       </c>
-      <c r="I20" t="s">
+      <c r="T20" t="s">
         <v>232</v>
       </c>
-      <c r="N20" t="s">
+      <c r="U20" t="s">
         <v>233</v>
       </c>
-      <c r="O20" t="s">
+      <c r="Z20" t="s">
         <v>234</v>
       </c>
-      <c r="T20" t="s">
+      <c r="AA20" t="s">
         <v>235</v>
       </c>
-      <c r="U20" t="s">
+      <c r="AF20" t="s">
         <v>236</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AG20" t="s">
+        <v>229</v>
+      </c>
+      <c r="AL20" t="s">
         <v>237</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AM20" t="s">
         <v>238</v>
       </c>
-      <c r="AF20" t="s">
+      <c r="AR20" t="s">
+        <v>232</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>233</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>234</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>235</v>
+      </c>
+      <c r="BD20" t="s">
         <v>239</v>
       </c>
-      <c r="AG20" t="s">
+      <c r="BE20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>240</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>241</v>
+      </c>
+      <c r="BP20" t="s">
         <v>232</v>
       </c>
-      <c r="AL20" t="s">
-        <v>240</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>241</v>
-      </c>
-      <c r="AR20" t="s">
+      <c r="BQ20" t="s">
+        <v>233</v>
+      </c>
+      <c r="BV20" t="s">
+        <v>234</v>
+      </c>
+      <c r="BW20" t="s">
         <v>235</v>
       </c>
-      <c r="AS20" t="s">
-        <v>236</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>237</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>238</v>
-      </c>
-      <c r="BD20" t="s">
+      <c r="CB20" t="s">
         <v>242</v>
       </c>
-      <c r="BE20" t="s">
+      <c r="CC20" t="s">
+        <v>229</v>
+      </c>
+      <c r="CH20" t="s">
+        <v>243</v>
+      </c>
+      <c r="CI20" t="s">
+        <v>244</v>
+      </c>
+      <c r="CN20" t="s">
         <v>232</v>
       </c>
-      <c r="BJ20" t="s">
-        <v>243</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>244</v>
-      </c>
-      <c r="BP20" t="s">
+      <c r="CO20" t="s">
+        <v>233</v>
+      </c>
+      <c r="CT20" t="s">
+        <v>234</v>
+      </c>
+      <c r="CU20" t="s">
         <v>235</v>
       </c>
-      <c r="BQ20" t="s">
-        <v>236</v>
-      </c>
-      <c r="BV20" t="s">
-        <v>237</v>
-      </c>
-      <c r="BW20" t="s">
-        <v>238</v>
-      </c>
-      <c r="CB20" t="s">
+      <c r="CZ20" t="s">
         <v>245</v>
       </c>
-      <c r="CC20" t="s">
-        <v>232</v>
-      </c>
-      <c r="CH20" t="s">
+      <c r="DA20" t="s">
         <v>246</v>
       </c>
-      <c r="CI20" t="s">
+      <c r="DF20" t="s">
         <v>247</v>
       </c>
-      <c r="CN20" t="s">
-        <v>235</v>
-      </c>
-      <c r="CO20" t="s">
-        <v>236</v>
-      </c>
-      <c r="CT20" t="s">
-        <v>237</v>
-      </c>
-      <c r="CU20" t="s">
-        <v>238</v>
-      </c>
-      <c r="CZ20" t="s">
+      <c r="DG20" t="s">
         <v>248</v>
       </c>
-      <c r="DA20" t="s">
+      <c r="DL20" t="s">
         <v>249</v>
       </c>
-      <c r="DF20" t="s">
+      <c r="DM20" t="s">
         <v>250</v>
       </c>
-      <c r="DG20" t="s">
+      <c r="DR20" t="s">
         <v>251</v>
       </c>
-      <c r="DL20" t="s">
+      <c r="DS20" t="s">
         <v>252</v>
       </c>
-      <c r="DM20" t="s">
+      <c r="DX20" t="s">
         <v>253</v>
       </c>
-      <c r="DR20" t="s">
+      <c r="DY20" t="s">
         <v>254</v>
       </c>
-      <c r="DS20" t="s">
+      <c r="ED20" t="s">
         <v>255</v>
       </c>
-      <c r="DX20" t="s">
+      <c r="EE20" t="s">
         <v>256</v>
       </c>
-      <c r="DY20" t="s">
+      <c r="EJ20" t="s">
         <v>257</v>
       </c>
-      <c r="ED20" t="s">
+      <c r="EK20" t="s">
         <v>258</v>
       </c>
-      <c r="EE20" t="s">
+      <c r="EP20" t="s">
         <v>259</v>
       </c>
-      <c r="EJ20" t="s">
+      <c r="EQ20" t="s">
         <v>260</v>
       </c>
-      <c r="EK20" t="s">
+      <c r="EV20" t="s">
         <v>261</v>
       </c>
-      <c r="EP20" t="s">
-        <v>262</v>
-      </c>
-      <c r="EQ20" t="s">
-        <v>263</v>
-      </c>
-      <c r="EV20" t="s">
-        <v>264</v>
-      </c>
       <c r="EW20" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:154">
       <c r="T21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="U21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Z21" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AA21" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AR21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AS21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AX21" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AY21" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="BP21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="BQ21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="BV21" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="BW21" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="CN21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="CO21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="CT21" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="CU21" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:154">
       <c r="A22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="M22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AE22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AK22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BC22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BI22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CA22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CG22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CY22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DE22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DK22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DQ22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DW22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EC22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EI22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EO22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EU22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:154">
       <c r="A23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="S23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="Y23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AE23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AK23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AW23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BC23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="BI23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="BO23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BU23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CA23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="CG23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="CM23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CS23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CY23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="DE23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="DK23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="DQ23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="DW23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="EC23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="EI23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="EO23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="EU23" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:154">
       <c r="B24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" t="s">
+        <v>271</v>
+      </c>
+      <c r="I24" t="s">
         <v>272</v>
       </c>
-      <c r="C24" t="s">
+      <c r="J24" t="s">
         <v>273</v>
       </c>
-      <c r="D24" t="s">
+      <c r="N24" t="s">
         <v>274</v>
       </c>
-      <c r="H24" t="s">
+      <c r="O24" t="s">
         <v>275</v>
       </c>
-      <c r="I24" t="s">
+      <c r="P24" t="s">
         <v>276</v>
       </c>
-      <c r="J24" t="s">
+      <c r="S24" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG24" t="s">
         <v>277</v>
       </c>
-      <c r="N24" t="s">
+      <c r="AH24" t="s">
         <v>278</v>
       </c>
-      <c r="O24" t="s">
+      <c r="AL24" t="s">
         <v>279</v>
       </c>
-      <c r="P24" t="s">
+      <c r="AM24" t="s">
         <v>280</v>
       </c>
-      <c r="S24" t="s">
+      <c r="AN24" t="s">
+        <v>281</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>267</v>
+      </c>
+      <c r="BD24" t="s">
         <v>271</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="BE24" t="s">
+        <v>277</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>273</v>
+      </c>
+      <c r="BJ24" t="s">
+        <v>282</v>
+      </c>
+      <c r="BK24" t="s">
+        <v>283</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>284</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>267</v>
+      </c>
+      <c r="BU24" t="s">
+        <v>267</v>
+      </c>
+      <c r="CB24" t="s">
         <v>271</v>
       </c>
-      <c r="AF24" t="s">
-        <v>275</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>281</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>282</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>283</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>284</v>
-      </c>
-      <c r="AN24" t="s">
+      <c r="CC24" t="s">
+        <v>272</v>
+      </c>
+      <c r="CD24" t="s">
+        <v>278</v>
+      </c>
+      <c r="CH24" t="s">
         <v>285</v>
       </c>
-      <c r="AQ24" t="s">
-        <v>271</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD24" t="s">
-        <v>275</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>281</v>
-      </c>
-      <c r="BF24" t="s">
-        <v>277</v>
-      </c>
-      <c r="BJ24" t="s">
+      <c r="CI24" t="s">
         <v>286</v>
       </c>
-      <c r="BK24" t="s">
+      <c r="CJ24" t="s">
         <v>287</v>
       </c>
-      <c r="BL24" t="s">
+      <c r="CM24" t="s">
+        <v>267</v>
+      </c>
+      <c r="CS24" t="s">
+        <v>267</v>
+      </c>
+      <c r="CZ24" t="s">
         <v>288</v>
       </c>
-      <c r="BO24" t="s">
-        <v>271</v>
-      </c>
-      <c r="BU24" t="s">
-        <v>271</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>275</v>
-      </c>
-      <c r="CC24" t="s">
-        <v>276</v>
-      </c>
-      <c r="CD24" t="s">
-        <v>282</v>
-      </c>
-      <c r="CH24" t="s">
+      <c r="DA24" t="s">
         <v>289</v>
       </c>
-      <c r="CI24" t="s">
+      <c r="DB24" t="s">
         <v>290</v>
       </c>
-      <c r="CJ24" t="s">
+      <c r="DF24" t="s">
         <v>291</v>
       </c>
-      <c r="CM24" t="s">
-        <v>271</v>
-      </c>
-      <c r="CS24" t="s">
-        <v>271</v>
-      </c>
-      <c r="CZ24" t="s">
+      <c r="DG24" t="s">
         <v>292</v>
       </c>
-      <c r="DA24" t="s">
+      <c r="DH24" t="s">
         <v>293</v>
       </c>
-      <c r="DB24" t="s">
+      <c r="DL24" t="s">
         <v>294</v>
       </c>
-      <c r="DF24" t="s">
+      <c r="DM24" t="s">
         <v>295</v>
       </c>
-      <c r="DG24" t="s">
+      <c r="DN24" t="s">
         <v>296</v>
       </c>
-      <c r="DH24" t="s">
+      <c r="DR24" t="s">
         <v>297</v>
       </c>
-      <c r="DL24" t="s">
+      <c r="DS24" t="s">
         <v>298</v>
       </c>
-      <c r="DM24" t="s">
+      <c r="DT24" t="s">
         <v>299</v>
       </c>
-      <c r="DN24" t="s">
+      <c r="DX24" t="s">
         <v>300</v>
       </c>
-      <c r="DR24" t="s">
+      <c r="DY24" t="s">
         <v>301</v>
       </c>
-      <c r="DS24" t="s">
+      <c r="DZ24" t="s">
         <v>302</v>
       </c>
-      <c r="DT24" t="s">
+      <c r="ED24" t="s">
         <v>303</v>
       </c>
-      <c r="DX24" t="s">
+      <c r="EE24" t="s">
         <v>304</v>
       </c>
-      <c r="DY24" t="s">
+      <c r="EF24" t="s">
         <v>305</v>
       </c>
-      <c r="DZ24" t="s">
+      <c r="EJ24" t="s">
         <v>306</v>
       </c>
-      <c r="ED24" t="s">
+      <c r="EK24" t="s">
         <v>307</v>
       </c>
-      <c r="EE24" t="s">
+      <c r="EL24" t="s">
         <v>308</v>
       </c>
-      <c r="EF24" t="s">
+      <c r="EP24" t="s">
         <v>309</v>
       </c>
-      <c r="EJ24" t="s">
+      <c r="EQ24" t="s">
         <v>310</v>
       </c>
-      <c r="EK24" t="s">
+      <c r="ER24" t="s">
         <v>311</v>
       </c>
-      <c r="EL24" t="s">
+      <c r="EV24" t="s">
+        <v>309</v>
+      </c>
+      <c r="EW24" t="s">
         <v>312</v>
       </c>
-      <c r="EP24" t="s">
+      <c r="EX24" t="s">
         <v>313</v>
-      </c>
-      <c r="EQ24" t="s">
-        <v>314</v>
-      </c>
-      <c r="ER24" t="s">
-        <v>315</v>
-      </c>
-      <c r="EV24" t="s">
-        <v>316</v>
-      </c>
-      <c r="EW24" t="s">
-        <v>317</v>
-      </c>
-      <c r="EX24" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:154">
       <c r="B25" t="s">
+        <v>314</v>
+      </c>
+      <c r="C25" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" t="s">
+        <v>316</v>
+      </c>
+      <c r="H25" t="s">
+        <v>317</v>
+      </c>
+      <c r="I25" t="s">
+        <v>318</v>
+      </c>
+      <c r="J25" t="s">
         <v>319</v>
       </c>
-      <c r="C25" t="s">
+      <c r="N25" t="s">
         <v>320</v>
       </c>
-      <c r="D25" t="s">
+      <c r="O25" t="s">
         <v>321</v>
       </c>
-      <c r="H25" t="s">
+      <c r="P25" t="s">
         <v>322</v>
       </c>
-      <c r="I25" t="s">
+      <c r="T25" t="s">
         <v>323</v>
       </c>
-      <c r="J25" t="s">
+      <c r="U25" t="s">
         <v>324</v>
       </c>
-      <c r="N25" t="s">
+      <c r="V25" t="s">
         <v>325</v>
       </c>
-      <c r="O25" t="s">
+      <c r="Z25" t="s">
         <v>326</v>
       </c>
-      <c r="P25" t="s">
+      <c r="AA25" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB25" t="s">
         <v>327</v>
       </c>
-      <c r="T25" t="s">
+      <c r="AF25" t="s">
         <v>328</v>
       </c>
-      <c r="U25" t="s">
+      <c r="AG25" t="s">
+        <v>318</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>319</v>
+      </c>
+      <c r="AL25" t="s">
         <v>329</v>
       </c>
-      <c r="V25" t="s">
+      <c r="AM25" t="s">
         <v>330</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AN25" t="s">
         <v>331</v>
       </c>
-      <c r="AA25" t="s">
-        <v>329</v>
-      </c>
-      <c r="AB25" t="s">
+      <c r="AR25" t="s">
+        <v>323</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>324</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>325</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>326</v>
+      </c>
+      <c r="AY25" t="s">
+        <v>324</v>
+      </c>
+      <c r="AZ25" t="s">
+        <v>327</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>328</v>
+      </c>
+      <c r="BE25" t="s">
+        <v>318</v>
+      </c>
+      <c r="BF25" t="s">
         <v>332</v>
       </c>
-      <c r="AF25" t="s">
+      <c r="BJ25" t="s">
         <v>333</v>
       </c>
-      <c r="AG25" t="s">
+      <c r="BK25" t="s">
+        <v>334</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>335</v>
+      </c>
+      <c r="BP25" t="s">
         <v>323</v>
       </c>
-      <c r="AH25" t="s">
+      <c r="BQ25" t="s">
         <v>324</v>
       </c>
-      <c r="AL25" t="s">
-        <v>334</v>
-      </c>
-      <c r="AM25" t="s">
-        <v>335</v>
-      </c>
-      <c r="AN25" t="s">
+      <c r="BR25" t="s">
+        <v>325</v>
+      </c>
+      <c r="BV25" t="s">
+        <v>326</v>
+      </c>
+      <c r="BW25" t="s">
+        <v>324</v>
+      </c>
+      <c r="BX25" t="s">
+        <v>327</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>317</v>
+      </c>
+      <c r="CC25" t="s">
+        <v>318</v>
+      </c>
+      <c r="CD25" t="s">
+        <v>332</v>
+      </c>
+      <c r="CH25" t="s">
         <v>336</v>
       </c>
-      <c r="AR25" t="s">
-        <v>328</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>329</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>330</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>331</v>
-      </c>
-      <c r="AY25" t="s">
-        <v>329</v>
-      </c>
-      <c r="AZ25" t="s">
-        <v>332</v>
-      </c>
-      <c r="BD25" t="s">
-        <v>333</v>
-      </c>
-      <c r="BE25" t="s">
+      <c r="CI25" t="s">
+        <v>337</v>
+      </c>
+      <c r="CJ25" t="s">
+        <v>338</v>
+      </c>
+      <c r="CN25" t="s">
         <v>323</v>
       </c>
-      <c r="BF25" t="s">
-        <v>337</v>
-      </c>
-      <c r="BJ25" t="s">
-        <v>338</v>
-      </c>
-      <c r="BK25" t="s">
+      <c r="CO25" t="s">
+        <v>324</v>
+      </c>
+      <c r="CP25" t="s">
+        <v>325</v>
+      </c>
+      <c r="CT25" t="s">
+        <v>326</v>
+      </c>
+      <c r="CU25" t="s">
+        <v>324</v>
+      </c>
+      <c r="CV25" t="s">
+        <v>327</v>
+      </c>
+      <c r="CZ25" t="s">
         <v>339</v>
       </c>
-      <c r="BL25" t="s">
+      <c r="DA25" t="s">
         <v>340</v>
       </c>
-      <c r="BP25" t="s">
-        <v>328</v>
-      </c>
-      <c r="BQ25" t="s">
-        <v>329</v>
-      </c>
-      <c r="BR25" t="s">
-        <v>330</v>
-      </c>
-      <c r="BV25" t="s">
-        <v>331</v>
-      </c>
-      <c r="BW25" t="s">
-        <v>329</v>
-      </c>
-      <c r="BX25" t="s">
-        <v>332</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>322</v>
-      </c>
-      <c r="CC25" t="s">
-        <v>323</v>
-      </c>
-      <c r="CD25" t="s">
-        <v>337</v>
-      </c>
-      <c r="CH25" t="s">
+      <c r="DB25" t="s">
         <v>341</v>
       </c>
-      <c r="CI25" t="s">
+      <c r="DF25" t="s">
         <v>342</v>
       </c>
-      <c r="CJ25" t="s">
+      <c r="DG25" t="s">
         <v>343</v>
       </c>
-      <c r="CN25" t="s">
-        <v>328</v>
-      </c>
-      <c r="CO25" t="s">
-        <v>329</v>
-      </c>
-      <c r="CP25" t="s">
-        <v>330</v>
-      </c>
-      <c r="CT25" t="s">
-        <v>331</v>
-      </c>
-      <c r="CU25" t="s">
-        <v>329</v>
-      </c>
-      <c r="CV25" t="s">
-        <v>332</v>
-      </c>
-      <c r="CZ25" t="s">
+      <c r="DH25" t="s">
         <v>344</v>
       </c>
-      <c r="DA25" t="s">
+      <c r="DL25" t="s">
         <v>345</v>
       </c>
-      <c r="DB25" t="s">
+      <c r="DM25" t="s">
         <v>346</v>
       </c>
-      <c r="DF25" t="s">
+      <c r="DN25" t="s">
         <v>347</v>
       </c>
-      <c r="DG25" t="s">
+      <c r="DR25" t="s">
         <v>348</v>
       </c>
-      <c r="DH25" t="s">
+      <c r="DS25" t="s">
         <v>349</v>
       </c>
-      <c r="DL25" t="s">
+      <c r="DT25" t="s">
         <v>350</v>
       </c>
-      <c r="DM25" t="s">
+      <c r="DX25" t="s">
         <v>351</v>
       </c>
-      <c r="DN25" t="s">
+      <c r="DY25" t="s">
         <v>352</v>
       </c>
-      <c r="DR25" t="s">
+      <c r="DZ25" t="s">
         <v>353</v>
       </c>
-      <c r="DS25" t="s">
+      <c r="ED25" t="s">
         <v>354</v>
       </c>
-      <c r="DT25" t="s">
+      <c r="EE25" t="s">
         <v>355</v>
       </c>
-      <c r="DX25" t="s">
+      <c r="EF25" t="s">
         <v>356</v>
       </c>
-      <c r="DY25" t="s">
+      <c r="EJ25" t="s">
         <v>357</v>
       </c>
-      <c r="DZ25" t="s">
+      <c r="EK25" t="s">
         <v>358</v>
       </c>
-      <c r="ED25" t="s">
+      <c r="EL25" t="s">
         <v>359</v>
       </c>
-      <c r="EE25" t="s">
+      <c r="EP25" t="s">
         <v>360</v>
       </c>
-      <c r="EF25" t="s">
+      <c r="EQ25" t="s">
         <v>361</v>
       </c>
-      <c r="EJ25" t="s">
+      <c r="ER25" t="s">
         <v>362</v>
       </c>
-      <c r="EK25" t="s">
+      <c r="EV25" t="s">
         <v>363</v>
       </c>
-      <c r="EL25" t="s">
-        <v>364</v>
-      </c>
-      <c r="EP25" t="s">
-        <v>365</v>
-      </c>
-      <c r="EQ25" t="s">
-        <v>366</v>
-      </c>
-      <c r="ER25" t="s">
-        <v>367</v>
-      </c>
-      <c r="EV25" t="s">
-        <v>368</v>
-      </c>
       <c r="EW25" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="EX25" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:154">
       <c r="B26" t="s">
+        <v>364</v>
+      </c>
+      <c r="C26" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" t="s">
+        <v>366</v>
+      </c>
+      <c r="H26" t="s">
+        <v>367</v>
+      </c>
+      <c r="I26" t="s">
+        <v>368</v>
+      </c>
+      <c r="J26" t="s">
+        <v>369</v>
+      </c>
+      <c r="N26" t="s">
+        <v>370</v>
+      </c>
+      <c r="O26" t="s">
         <v>371</v>
       </c>
-      <c r="C26" t="s">
+      <c r="P26" t="s">
         <v>372</v>
       </c>
-      <c r="D26" t="s">
+      <c r="T26" t="s">
         <v>373</v>
       </c>
-      <c r="H26" t="s">
+      <c r="U26" t="s">
         <v>374</v>
       </c>
-      <c r="I26" t="s">
+      <c r="V26" t="s">
         <v>375</v>
       </c>
-      <c r="J26" t="s">
+      <c r="Z26" t="s">
+        <v>373</v>
+      </c>
+      <c r="AA26" t="s">
         <v>376</v>
       </c>
-      <c r="N26" t="s">
+      <c r="AB26" t="s">
         <v>377</v>
       </c>
-      <c r="O26" t="s">
+      <c r="AF26" t="s">
         <v>378</v>
       </c>
-      <c r="P26" t="s">
+      <c r="AG26" t="s">
+        <v>368</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL26" t="s">
         <v>379</v>
       </c>
-      <c r="T26" t="s">
+      <c r="AM26" t="s">
         <v>380</v>
       </c>
-      <c r="U26" t="s">
+      <c r="AN26" t="s">
         <v>381</v>
       </c>
-      <c r="V26" t="s">
+      <c r="AR26" t="s">
+        <v>373</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>374</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>375</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>373</v>
+      </c>
+      <c r="AY26" t="s">
+        <v>376</v>
+      </c>
+      <c r="AZ26" t="s">
+        <v>377</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>367</v>
+      </c>
+      <c r="BE26" t="s">
         <v>382</v>
       </c>
-      <c r="Z26" t="s">
-        <v>380</v>
-      </c>
-      <c r="AA26" t="s">
+      <c r="BF26" t="s">
+        <v>369</v>
+      </c>
+      <c r="BJ26" t="s">
         <v>383</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="BK26" t="s">
         <v>384</v>
       </c>
-      <c r="AF26" t="s">
+      <c r="BL26" t="s">
         <v>385</v>
       </c>
-      <c r="AG26" t="s">
+      <c r="BP26" t="s">
+        <v>373</v>
+      </c>
+      <c r="BQ26" t="s">
+        <v>374</v>
+      </c>
+      <c r="BR26" t="s">
         <v>375</v>
       </c>
-      <c r="AH26" t="s">
+      <c r="BV26" t="s">
+        <v>373</v>
+      </c>
+      <c r="BW26" t="s">
         <v>376</v>
       </c>
-      <c r="AL26" t="s">
+      <c r="BX26" t="s">
+        <v>377</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>378</v>
+      </c>
+      <c r="CC26" t="s">
+        <v>382</v>
+      </c>
+      <c r="CD26" t="s">
+        <v>369</v>
+      </c>
+      <c r="CH26" t="s">
         <v>386</v>
       </c>
-      <c r="AM26" t="s">
+      <c r="CI26" t="s">
         <v>387</v>
       </c>
-      <c r="AN26" t="s">
+      <c r="CJ26" t="s">
         <v>388</v>
       </c>
-      <c r="AR26" t="s">
-        <v>380</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>381</v>
-      </c>
-      <c r="AT26" t="s">
-        <v>382</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>380</v>
-      </c>
-      <c r="AY26" t="s">
-        <v>383</v>
-      </c>
-      <c r="AZ26" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD26" t="s">
+      <c r="CN26" t="s">
+        <v>373</v>
+      </c>
+      <c r="CO26" t="s">
         <v>374</v>
       </c>
-      <c r="BE26" t="s">
+      <c r="CP26" t="s">
+        <v>375</v>
+      </c>
+      <c r="CT26" t="s">
+        <v>373</v>
+      </c>
+      <c r="CU26" t="s">
+        <v>376</v>
+      </c>
+      <c r="CV26" t="s">
+        <v>377</v>
+      </c>
+      <c r="CZ26" t="s">
         <v>389</v>
       </c>
-      <c r="BF26" t="s">
-        <v>376</v>
-      </c>
-      <c r="BJ26" t="s">
+      <c r="DA26" t="s">
         <v>390</v>
       </c>
-      <c r="BK26" t="s">
+      <c r="DB26" t="s">
         <v>391</v>
       </c>
-      <c r="BL26" t="s">
+      <c r="DF26" t="s">
         <v>392</v>
       </c>
-      <c r="BP26" t="s">
-        <v>380</v>
-      </c>
-      <c r="BQ26" t="s">
-        <v>381</v>
-      </c>
-      <c r="BR26" t="s">
-        <v>382</v>
-      </c>
-      <c r="BV26" t="s">
-        <v>380</v>
-      </c>
-      <c r="BW26" t="s">
-        <v>383</v>
-      </c>
-      <c r="BX26" t="s">
-        <v>384</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>385</v>
-      </c>
-      <c r="CC26" t="s">
-        <v>389</v>
-      </c>
-      <c r="CD26" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH26" t="s">
+      <c r="DG26" t="s">
         <v>393</v>
       </c>
-      <c r="CI26" t="s">
+      <c r="DH26" t="s">
         <v>394</v>
       </c>
-      <c r="CJ26" t="s">
+      <c r="DL26" t="s">
         <v>395</v>
       </c>
-      <c r="CN26" t="s">
-        <v>380</v>
-      </c>
-      <c r="CO26" t="s">
-        <v>381</v>
-      </c>
-      <c r="CP26" t="s">
-        <v>382</v>
-      </c>
-      <c r="CT26" t="s">
-        <v>380</v>
-      </c>
-      <c r="CU26" t="s">
-        <v>383</v>
-      </c>
-      <c r="CV26" t="s">
-        <v>384</v>
-      </c>
-      <c r="CZ26" t="s">
+      <c r="DM26" t="s">
         <v>396</v>
       </c>
-      <c r="DA26" t="s">
+      <c r="DN26" t="s">
         <v>397</v>
       </c>
-      <c r="DB26" t="s">
+      <c r="DR26" t="s">
         <v>398</v>
       </c>
-      <c r="DF26" t="s">
+      <c r="DS26" t="s">
         <v>399</v>
       </c>
-      <c r="DG26" t="s">
+      <c r="DT26" t="s">
         <v>400</v>
       </c>
-      <c r="DH26" t="s">
+      <c r="DX26" t="s">
         <v>401</v>
       </c>
-      <c r="DL26" t="s">
+      <c r="DY26" t="s">
         <v>402</v>
       </c>
-      <c r="DM26" t="s">
+      <c r="DZ26" t="s">
         <v>403</v>
       </c>
-      <c r="DN26" t="s">
+      <c r="ED26" t="s">
         <v>404</v>
       </c>
-      <c r="DR26" t="s">
+      <c r="EE26" t="s">
         <v>405</v>
       </c>
-      <c r="DS26" t="s">
+      <c r="EF26" t="s">
         <v>406</v>
       </c>
-      <c r="DT26" t="s">
+      <c r="EJ26" t="s">
         <v>407</v>
       </c>
-      <c r="DX26" t="s">
+      <c r="EK26" t="s">
         <v>408</v>
       </c>
-      <c r="DY26" t="s">
+      <c r="EL26" t="s">
         <v>409</v>
       </c>
-      <c r="DZ26" t="s">
+      <c r="EP26" t="s">
         <v>410</v>
       </c>
-      <c r="ED26" t="s">
+      <c r="EQ26" t="s">
         <v>411</v>
       </c>
-      <c r="EE26" t="s">
+      <c r="ER26" t="s">
         <v>412</v>
       </c>
-      <c r="EF26" t="s">
+      <c r="EV26" t="s">
         <v>413</v>
       </c>
-      <c r="EJ26" t="s">
-        <v>414</v>
-      </c>
-      <c r="EK26" t="s">
-        <v>415</v>
-      </c>
-      <c r="EL26" t="s">
-        <v>416</v>
-      </c>
-      <c r="EP26" t="s">
-        <v>417</v>
-      </c>
-      <c r="EQ26" t="s">
-        <v>418</v>
-      </c>
-      <c r="ER26" t="s">
-        <v>419</v>
-      </c>
-      <c r="EV26" t="s">
-        <v>420</v>
-      </c>
       <c r="EW26" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="EX26" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:154">
       <c r="T27" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="U27" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="V27" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="Z27" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AA27" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AB27" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AR27" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AS27" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AT27" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AX27" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AY27" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AZ27" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="BP27" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="BQ27" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="BR27" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="BV27" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="BW27" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="BX27" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="CN27" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="CO27" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="CP27" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="CT27" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="CU27" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="CV27" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="1:154">
       <c r="A28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AE28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AK28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BC28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BI28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CA28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CG28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CY28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DE28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DK28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DQ28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="DW28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EC28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EI28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EO28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="EU28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:154">
       <c r="A29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="M29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="S29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="Y29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AE29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AK29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AQ29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AW29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BC29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="BI29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="BO29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BU29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CA29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="CG29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="CM29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CS29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CY29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="DE29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="DK29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="DQ29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="DW29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="EC29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="EI29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="EO29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="EU29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:154">
       <c r="B30" t="s">
+        <v>421</v>
+      </c>
+      <c r="C30" t="s">
+        <v>422</v>
+      </c>
+      <c r="D30" t="s">
+        <v>423</v>
+      </c>
+      <c r="H30" t="s">
+        <v>424</v>
+      </c>
+      <c r="I30" t="s">
+        <v>425</v>
+      </c>
+      <c r="J30" t="s">
+        <v>426</v>
+      </c>
+      <c r="N30" t="s">
+        <v>427</v>
+      </c>
+      <c r="O30" t="s">
+        <v>428</v>
+      </c>
+      <c r="P30" t="s">
         <v>429</v>
       </c>
-      <c r="C30" t="s">
+      <c r="S30" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>420</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>424</v>
+      </c>
+      <c r="AG30" t="s">
         <v>430</v>
       </c>
-      <c r="D30" t="s">
+      <c r="AH30" t="s">
         <v>431</v>
       </c>
-      <c r="H30" t="s">
+      <c r="AL30" t="s">
         <v>432</v>
       </c>
-      <c r="I30" t="s">
+      <c r="AM30" t="s">
         <v>433</v>
       </c>
-      <c r="J30" t="s">
+      <c r="AN30" t="s">
         <v>434</v>
       </c>
-      <c r="N30" t="s">
+      <c r="AQ30" t="s">
+        <v>420</v>
+      </c>
+      <c r="AW30" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD30" t="s">
+        <v>424</v>
+      </c>
+      <c r="BE30" t="s">
+        <v>430</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>426</v>
+      </c>
+      <c r="BJ30" t="s">
         <v>435</v>
       </c>
-      <c r="O30" t="s">
+      <c r="BK30" t="s">
         <v>436</v>
       </c>
-      <c r="P30" t="s">
+      <c r="BL30" t="s">
         <v>437</v>
       </c>
-      <c r="S30" t="s">
-        <v>428</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>428</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>432</v>
-      </c>
-      <c r="AG30" t="s">
+      <c r="BO30" t="s">
+        <v>420</v>
+      </c>
+      <c r="BU30" t="s">
+        <v>420</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>424</v>
+      </c>
+      <c r="CC30" t="s">
+        <v>425</v>
+      </c>
+      <c r="CD30" t="s">
+        <v>431</v>
+      </c>
+      <c r="CH30" t="s">
         <v>438</v>
       </c>
-      <c r="AH30" t="s">
+      <c r="CI30" t="s">
         <v>439</v>
       </c>
-      <c r="AL30" t="s">
+      <c r="CJ30" t="s">
         <v>440</v>
       </c>
-      <c r="AM30" t="s">
+      <c r="CM30" t="s">
+        <v>420</v>
+      </c>
+      <c r="CS30" t="s">
+        <v>420</v>
+      </c>
+      <c r="CZ30" t="s">
         <v>441</v>
       </c>
-      <c r="AN30" t="s">
+      <c r="DA30" t="s">
         <v>442</v>
       </c>
-      <c r="AQ30" t="s">
-        <v>428</v>
-      </c>
-      <c r="AW30" t="s">
-        <v>428</v>
-      </c>
-      <c r="BD30" t="s">
-        <v>432</v>
-      </c>
-      <c r="BE30" t="s">
-        <v>438</v>
-      </c>
-      <c r="BF30" t="s">
-        <v>434</v>
-      </c>
-      <c r="BJ30" t="s">
+      <c r="DB30" t="s">
         <v>443</v>
       </c>
-      <c r="BK30" t="s">
+      <c r="DF30" t="s">
         <v>444</v>
       </c>
-      <c r="BL30" t="s">
+      <c r="DG30" t="s">
         <v>445</v>
       </c>
-      <c r="BO30" t="s">
-        <v>428</v>
-      </c>
-      <c r="BU30" t="s">
-        <v>428</v>
-      </c>
-      <c r="CB30" t="s">
-        <v>432</v>
-      </c>
-      <c r="CC30" t="s">
-        <v>433</v>
-      </c>
-      <c r="CD30" t="s">
-        <v>439</v>
-      </c>
-      <c r="CH30" t="s">
+      <c r="DH30" t="s">
         <v>446</v>
       </c>
-      <c r="CI30" t="s">
+      <c r="DL30" t="s">
         <v>447</v>
       </c>
-      <c r="CJ30" t="s">
+      <c r="DM30" t="s">
         <v>448</v>
       </c>
-      <c r="CM30" t="s">
-        <v>428</v>
-      </c>
-      <c r="CS30" t="s">
-        <v>428</v>
-      </c>
-      <c r="CZ30" t="s">
+      <c r="DN30" t="s">
         <v>449</v>
       </c>
-      <c r="DA30" t="s">
+      <c r="DR30" t="s">
         <v>450</v>
       </c>
-      <c r="DB30" t="s">
+      <c r="DS30" t="s">
         <v>451</v>
       </c>
-      <c r="DF30" t="s">
+      <c r="DT30" t="s">
         <v>452</v>
       </c>
-      <c r="DG30" t="s">
+      <c r="DX30" t="s">
         <v>453</v>
       </c>
-      <c r="DH30" t="s">
+      <c r="DY30" t="s">
         <v>454</v>
       </c>
-      <c r="DL30" t="s">
+      <c r="DZ30" t="s">
         <v>455</v>
       </c>
-      <c r="DM30" t="s">
+      <c r="ED30" t="s">
         <v>456</v>
       </c>
-      <c r="DN30" t="s">
+      <c r="EE30" t="s">
         <v>457</v>
       </c>
-      <c r="DR30" t="s">
+      <c r="EF30" t="s">
         <v>458</v>
       </c>
-      <c r="DS30" t="s">
+      <c r="EJ30" t="s">
         <v>459</v>
       </c>
-      <c r="DT30" t="s">
+      <c r="EK30" t="s">
         <v>460</v>
       </c>
-      <c r="DX30" t="s">
+      <c r="EL30" t="s">
         <v>461</v>
       </c>
-      <c r="DY30" t="s">
+      <c r="EP30" t="s">
         <v>462</v>
       </c>
-      <c r="DZ30" t="s">
+      <c r="EQ30" t="s">
         <v>463</v>
       </c>
-      <c r="ED30" t="s">
+      <c r="ER30" t="s">
         <v>464</v>
       </c>
-      <c r="EE30" t="s">
+      <c r="EV30" t="s">
+        <v>462</v>
+      </c>
+      <c r="EW30" t="s">
         <v>465</v>
       </c>
-      <c r="EF30" t="s">
+      <c r="EX30" t="s">
         <v>466</v>
-      </c>
-      <c r="EJ30" t="s">
-        <v>467</v>
-      </c>
-      <c r="EK30" t="s">
-        <v>468</v>
-      </c>
-      <c r="EL30" t="s">
-        <v>469</v>
-      </c>
-      <c r="EP30" t="s">
-        <v>470</v>
-      </c>
-      <c r="EQ30" t="s">
-        <v>471</v>
-      </c>
-      <c r="ER30" t="s">
-        <v>472</v>
-      </c>
-      <c r="EV30" t="s">
-        <v>470</v>
-      </c>
-      <c r="EW30" t="s">
-        <v>473</v>
-      </c>
-      <c r="EX30" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:154">
       <c r="B31" t="s">
+        <v>467</v>
+      </c>
+      <c r="C31" t="s">
+        <v>468</v>
+      </c>
+      <c r="D31" t="s">
+        <v>469</v>
+      </c>
+      <c r="H31" t="s">
+        <v>470</v>
+      </c>
+      <c r="I31" t="s">
+        <v>471</v>
+      </c>
+      <c r="J31" t="s">
+        <v>472</v>
+      </c>
+      <c r="N31" t="s">
+        <v>473</v>
+      </c>
+      <c r="O31" t="s">
+        <v>474</v>
+      </c>
+      <c r="P31" t="s">
         <v>475</v>
       </c>
-      <c r="C31" t="s">
+      <c r="T31" t="s">
         <v>476</v>
       </c>
-      <c r="D31" t="s">
+      <c r="U31" t="s">
+        <v>457</v>
+      </c>
+      <c r="V31" t="s">
         <v>477</v>
       </c>
-      <c r="H31" t="s">
+      <c r="Z31" t="s">
         <v>478</v>
       </c>
-      <c r="I31" t="s">
+      <c r="AA31" t="s">
+        <v>457</v>
+      </c>
+      <c r="AB31" t="s">
         <v>479</v>
       </c>
-      <c r="J31" t="s">
+      <c r="AF31" t="s">
         <v>480</v>
       </c>
-      <c r="N31" t="s">
+      <c r="AG31" t="s">
+        <v>471</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>472</v>
+      </c>
+      <c r="AL31" t="s">
         <v>481</v>
       </c>
-      <c r="O31" t="s">
+      <c r="AM31" t="s">
+        <v>474</v>
+      </c>
+      <c r="AN31" t="s">
         <v>482</v>
       </c>
-      <c r="P31" t="s">
+      <c r="AR31" t="s">
+        <v>476</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>457</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>477</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>478</v>
+      </c>
+      <c r="AY31" t="s">
+        <v>457</v>
+      </c>
+      <c r="AZ31" t="s">
+        <v>479</v>
+      </c>
+      <c r="BD31" t="s">
+        <v>480</v>
+      </c>
+      <c r="BE31" t="s">
+        <v>471</v>
+      </c>
+      <c r="BF31" t="s">
         <v>483</v>
       </c>
-      <c r="T31" t="s">
+      <c r="BJ31" t="s">
         <v>484</v>
       </c>
-      <c r="U31" t="s">
-        <v>465</v>
-      </c>
-      <c r="V31" t="s">
+      <c r="BK31" t="s">
+        <v>474</v>
+      </c>
+      <c r="BL31" t="s">
         <v>485</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="BP31" t="s">
+        <v>476</v>
+      </c>
+      <c r="BQ31" t="s">
+        <v>457</v>
+      </c>
+      <c r="BR31" t="s">
+        <v>477</v>
+      </c>
+      <c r="BV31" t="s">
+        <v>478</v>
+      </c>
+      <c r="BW31" t="s">
+        <v>457</v>
+      </c>
+      <c r="BX31" t="s">
+        <v>479</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>470</v>
+      </c>
+      <c r="CC31" t="s">
+        <v>471</v>
+      </c>
+      <c r="CD31" t="s">
+        <v>483</v>
+      </c>
+      <c r="CH31" t="s">
         <v>486</v>
       </c>
-      <c r="AA31" t="s">
-        <v>465</v>
-      </c>
-      <c r="AB31" t="s">
+      <c r="CI31" t="s">
+        <v>474</v>
+      </c>
+      <c r="CJ31" t="s">
         <v>487</v>
       </c>
-      <c r="AF31" t="s">
+      <c r="CN31" t="s">
+        <v>476</v>
+      </c>
+      <c r="CO31" t="s">
+        <v>457</v>
+      </c>
+      <c r="CP31" t="s">
+        <v>477</v>
+      </c>
+      <c r="CT31" t="s">
+        <v>478</v>
+      </c>
+      <c r="CU31" t="s">
+        <v>457</v>
+      </c>
+      <c r="CV31" t="s">
+        <v>479</v>
+      </c>
+      <c r="CZ31" t="s">
         <v>488</v>
       </c>
-      <c r="AG31" t="s">
-        <v>479</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>480</v>
-      </c>
-      <c r="AL31" t="s">
+      <c r="DA31" t="s">
         <v>489</v>
       </c>
-      <c r="AM31" t="s">
-        <v>482</v>
-      </c>
-      <c r="AN31" t="s">
+      <c r="DB31" t="s">
         <v>490</v>
       </c>
-      <c r="AR31" t="s">
-        <v>484</v>
-      </c>
-      <c r="AS31" t="s">
-        <v>465</v>
-      </c>
-      <c r="AT31" t="s">
-        <v>485</v>
-      </c>
-      <c r="AX31" t="s">
-        <v>486</v>
-      </c>
-      <c r="AY31" t="s">
-        <v>465</v>
-      </c>
-      <c r="AZ31" t="s">
-        <v>487</v>
-      </c>
-      <c r="BD31" t="s">
-        <v>488</v>
-      </c>
-      <c r="BE31" t="s">
-        <v>479</v>
-      </c>
-      <c r="BF31" t="s">
+      <c r="DF31" t="s">
         <v>491</v>
       </c>
-      <c r="BJ31" t="s">
+      <c r="DG31" t="s">
         <v>492</v>
       </c>
-      <c r="BK31" t="s">
-        <v>482</v>
-      </c>
-      <c r="BL31" t="s">
+      <c r="DH31" t="s">
         <v>493</v>
       </c>
-      <c r="BP31" t="s">
-        <v>484</v>
-      </c>
-      <c r="BQ31" t="s">
-        <v>465</v>
-      </c>
-      <c r="BR31" t="s">
-        <v>485</v>
-      </c>
-      <c r="BV31" t="s">
-        <v>486</v>
-      </c>
-      <c r="BW31" t="s">
-        <v>465</v>
-      </c>
-      <c r="BX31" t="s">
-        <v>487</v>
-      </c>
-      <c r="CB31" t="s">
-        <v>478</v>
-      </c>
-      <c r="CC31" t="s">
-        <v>479</v>
-      </c>
-      <c r="CD31" t="s">
-        <v>491</v>
-      </c>
-      <c r="CH31" t="s">
+      <c r="DL31" t="s">
         <v>494</v>
       </c>
-      <c r="CI31" t="s">
-        <v>482</v>
-      </c>
-      <c r="CJ31" t="s">
+      <c r="DM31" t="s">
         <v>495</v>
       </c>
-      <c r="CN31" t="s">
-        <v>484</v>
-      </c>
-      <c r="CO31" t="s">
-        <v>465</v>
-      </c>
-      <c r="CP31" t="s">
-        <v>485</v>
-      </c>
-      <c r="CT31" t="s">
-        <v>486</v>
-      </c>
-      <c r="CU31" t="s">
-        <v>465</v>
-      </c>
-      <c r="CV31" t="s">
-        <v>487</v>
-      </c>
-      <c r="CZ31" t="s">
+      <c r="DN31" t="s">
         <v>496</v>
       </c>
-      <c r="DA31" t="s">
+      <c r="DR31" t="s">
         <v>497</v>
       </c>
-      <c r="DB31" t="s">
+      <c r="DS31" t="s">
         <v>498</v>
       </c>
-      <c r="DF31" t="s">
+      <c r="DT31" t="s">
         <v>499</v>
       </c>
-      <c r="DG31" t="s">
+      <c r="DX31" t="s">
         <v>500</v>
       </c>
-      <c r="DH31" t="s">
+      <c r="DY31" t="s">
         <v>501</v>
       </c>
-      <c r="DL31" t="s">
+      <c r="DZ31" t="s">
         <v>502</v>
       </c>
-      <c r="DM31" t="s">
+      <c r="ED31" t="s">
         <v>503</v>
       </c>
-      <c r="DN31" t="s">
+      <c r="EE31" t="s">
         <v>504</v>
       </c>
-      <c r="DR31" t="s">
+      <c r="EF31" t="s">
         <v>505</v>
       </c>
-      <c r="DS31" t="s">
+      <c r="EJ31" t="s">
         <v>506</v>
       </c>
-      <c r="DT31" t="s">
+      <c r="EK31" t="s">
         <v>507</v>
       </c>
-      <c r="DX31" t="s">
+      <c r="EL31" t="s">
         <v>508</v>
       </c>
-      <c r="DY31" t="s">
+      <c r="EP31" t="s">
         <v>509</v>
       </c>
-      <c r="DZ31" t="s">
+      <c r="EQ31" t="s">
         <v>510</v>
       </c>
-      <c r="ED31" t="s">
+      <c r="ER31" t="s">
         <v>511</v>
       </c>
-      <c r="EE31" t="s">
+      <c r="EV31" t="s">
         <v>512</v>
       </c>
-      <c r="EF31" t="s">
-        <v>513</v>
-      </c>
-      <c r="EJ31" t="s">
-        <v>514</v>
-      </c>
-      <c r="EK31" t="s">
-        <v>515</v>
-      </c>
-      <c r="EL31" t="s">
-        <v>516</v>
-      </c>
-      <c r="EP31" t="s">
-        <v>517</v>
-      </c>
-      <c r="EQ31" t="s">
-        <v>518</v>
-      </c>
-      <c r="ER31" t="s">
-        <v>519</v>
-      </c>
-      <c r="EV31" t="s">
-        <v>520</v>
-      </c>
       <c r="EW31" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="EX31" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="32" spans="1:154">
       <c r="B32" t="s">
+        <v>513</v>
+      </c>
+      <c r="C32" t="s">
+        <v>514</v>
+      </c>
+      <c r="D32" t="s">
+        <v>515</v>
+      </c>
+      <c r="H32" t="s">
+        <v>516</v>
+      </c>
+      <c r="I32" t="s">
+        <v>517</v>
+      </c>
+      <c r="J32" t="s">
+        <v>518</v>
+      </c>
+      <c r="N32" t="s">
+        <v>519</v>
+      </c>
+      <c r="O32" t="s">
+        <v>520</v>
+      </c>
+      <c r="P32" t="s">
+        <v>521</v>
+      </c>
+      <c r="T32" t="s">
+        <v>503</v>
+      </c>
+      <c r="U32" t="s">
         <v>522</v>
       </c>
-      <c r="C32" t="s">
+      <c r="V32" t="s">
         <v>523</v>
       </c>
-      <c r="D32" t="s">
+      <c r="Z32" t="s">
+        <v>503</v>
+      </c>
+      <c r="AA32" t="s">
         <v>524</v>
       </c>
-      <c r="H32" t="s">
+      <c r="AB32" t="s">
+        <v>523</v>
+      </c>
+      <c r="AF32" t="s">
         <v>525</v>
       </c>
-      <c r="I32" t="s">
+      <c r="AG32" t="s">
+        <v>517</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>518</v>
+      </c>
+      <c r="AL32" t="s">
         <v>526</v>
       </c>
-      <c r="J32" t="s">
+      <c r="AM32" t="s">
         <v>527</v>
       </c>
-      <c r="N32" t="s">
+      <c r="AN32" t="s">
         <v>528</v>
       </c>
-      <c r="O32" t="s">
+      <c r="AR32" t="s">
+        <v>503</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>522</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>523</v>
+      </c>
+      <c r="AX32" t="s">
+        <v>503</v>
+      </c>
+      <c r="AY32" t="s">
+        <v>524</v>
+      </c>
+      <c r="AZ32" t="s">
+        <v>523</v>
+      </c>
+      <c r="BD32" t="s">
+        <v>516</v>
+      </c>
+      <c r="BE32" t="s">
         <v>529</v>
       </c>
-      <c r="P32" t="s">
+      <c r="BF32" t="s">
+        <v>518</v>
+      </c>
+      <c r="BJ32" t="s">
         <v>530</v>
       </c>
-      <c r="T32" t="s">
-        <v>511</v>
-      </c>
-      <c r="U32" t="s">
+      <c r="BK32" t="s">
         <v>531</v>
       </c>
-      <c r="V32" t="s">
+      <c r="BL32" t="s">
         <v>532</v>
       </c>
-      <c r="Z32" t="s">
-        <v>511</v>
-      </c>
-      <c r="AA32" t="s">
+      <c r="BP32" t="s">
+        <v>503</v>
+      </c>
+      <c r="BQ32" t="s">
+        <v>522</v>
+      </c>
+      <c r="BR32" t="s">
+        <v>523</v>
+      </c>
+      <c r="BV32" t="s">
+        <v>503</v>
+      </c>
+      <c r="BW32" t="s">
+        <v>524</v>
+      </c>
+      <c r="BX32" t="s">
+        <v>523</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>525</v>
+      </c>
+      <c r="CC32" t="s">
+        <v>529</v>
+      </c>
+      <c r="CD32" t="s">
+        <v>518</v>
+      </c>
+      <c r="CH32" t="s">
         <v>533</v>
       </c>
-      <c r="AB32" t="s">
-        <v>532</v>
-      </c>
-      <c r="AF32" t="s">
+      <c r="CI32" t="s">
         <v>534</v>
       </c>
-      <c r="AG32" t="s">
-        <v>526</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>527</v>
-      </c>
-      <c r="AL32" t="s">
+      <c r="CJ32" t="s">
         <v>535</v>
       </c>
-      <c r="AM32" t="s">
+      <c r="CN32" t="s">
+        <v>503</v>
+      </c>
+      <c r="CO32" t="s">
+        <v>522</v>
+      </c>
+      <c r="CP32" t="s">
+        <v>523</v>
+      </c>
+      <c r="CT32" t="s">
+        <v>503</v>
+      </c>
+      <c r="CU32" t="s">
+        <v>524</v>
+      </c>
+      <c r="CV32" t="s">
+        <v>523</v>
+      </c>
+      <c r="CZ32" t="s">
         <v>536</v>
       </c>
-      <c r="AN32" t="s">
+      <c r="DA32" t="s">
         <v>537</v>
       </c>
-      <c r="AR32" t="s">
-        <v>511</v>
-      </c>
-      <c r="AS32" t="s">
-        <v>531</v>
-      </c>
-      <c r="AT32" t="s">
-        <v>532</v>
-      </c>
-      <c r="AX32" t="s">
-        <v>511</v>
-      </c>
-      <c r="AY32" t="s">
-        <v>533</v>
-      </c>
-      <c r="AZ32" t="s">
-        <v>532</v>
-      </c>
-      <c r="BD32" t="s">
-        <v>525</v>
-      </c>
-      <c r="BE32" t="s">
+      <c r="DB32" t="s">
         <v>538</v>
       </c>
-      <c r="BF32" t="s">
-        <v>527</v>
-      </c>
-      <c r="BJ32" t="s">
+      <c r="DF32" t="s">
         <v>539</v>
       </c>
-      <c r="BK32" t="s">
+      <c r="DG32" t="s">
         <v>540</v>
       </c>
-      <c r="BL32" t="s">
+      <c r="DH32" t="s">
         <v>541</v>
       </c>
-      <c r="BP32" t="s">
-        <v>511</v>
-      </c>
-      <c r="BQ32" t="s">
-        <v>531</v>
-      </c>
-      <c r="BR32" t="s">
-        <v>532</v>
-      </c>
-      <c r="BV32" t="s">
-        <v>511</v>
-      </c>
-      <c r="BW32" t="s">
-        <v>533</v>
-      </c>
-      <c r="BX32" t="s">
-        <v>532</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>534</v>
-      </c>
-      <c r="CC32" t="s">
-        <v>538</v>
-      </c>
-      <c r="CD32" t="s">
-        <v>527</v>
-      </c>
-      <c r="CH32" t="s">
+      <c r="DL32" t="s">
         <v>542</v>
       </c>
-      <c r="CI32" t="s">
+      <c r="DM32" t="s">
         <v>543</v>
       </c>
-      <c r="CJ32" t="s">
+      <c r="DN32" t="s">
         <v>544</v>
       </c>
-      <c r="CN32" t="s">
-        <v>511</v>
-      </c>
-      <c r="CO32" t="s">
-        <v>531</v>
-      </c>
-      <c r="CP32" t="s">
-        <v>532</v>
-      </c>
-      <c r="CT32" t="s">
-        <v>511</v>
-      </c>
-      <c r="CU32" t="s">
-        <v>533</v>
-      </c>
-      <c r="CV32" t="s">
-        <v>532</v>
-      </c>
-      <c r="CZ32" t="s">
+      <c r="DR32" t="s">
         <v>545</v>
       </c>
-      <c r="DA32" t="s">
+      <c r="DS32" t="s">
         <v>546</v>
       </c>
-      <c r="DB32" t="s">
+      <c r="DT32" t="s">
         <v>547</v>
       </c>
-      <c r="DF32" t="s">
+      <c r="DX32" t="s">
         <v>548</v>
       </c>
-      <c r="DG32" t="s">
+      <c r="DY32" t="s">
         <v>549</v>
       </c>
-      <c r="DH32" t="s">
+      <c r="DZ32" t="s">
         <v>550</v>
       </c>
-      <c r="DL32" t="s">
+      <c r="ED32" t="s">
         <v>551</v>
       </c>
-      <c r="DM32" t="s">
+      <c r="EE32" t="s">
         <v>552</v>
       </c>
-      <c r="DN32" t="s">
+      <c r="EF32" t="s">
         <v>553</v>
       </c>
-      <c r="DR32" t="s">
+      <c r="EJ32" t="s">
         <v>554</v>
       </c>
-      <c r="DS32" t="s">
+      <c r="EK32" t="s">
         <v>555</v>
       </c>
-      <c r="DT32" t="s">
+      <c r="EL32" t="s">
         <v>556</v>
       </c>
-      <c r="DX32" t="s">
+      <c r="EP32" t="s">
         <v>557</v>
       </c>
-      <c r="DY32" t="s">
+      <c r="EQ32" t="s">
         <v>558</v>
       </c>
-      <c r="DZ32" t="s">
+      <c r="ER32" t="s">
         <v>559</v>
       </c>
-      <c r="ED32" t="s">
+      <c r="EV32" t="s">
         <v>560</v>
       </c>
-      <c r="EE32" t="s">
-        <v>561</v>
-      </c>
-      <c r="EF32" t="s">
-        <v>562</v>
-      </c>
-      <c r="EJ32" t="s">
-        <v>563</v>
-      </c>
-      <c r="EK32" t="s">
-        <v>564</v>
-      </c>
-      <c r="EL32" t="s">
-        <v>565</v>
-      </c>
-      <c r="EP32" t="s">
-        <v>566</v>
-      </c>
-      <c r="EQ32" t="s">
-        <v>567</v>
-      </c>
-      <c r="ER32" t="s">
-        <v>568</v>
-      </c>
-      <c r="EV32" t="s">
-        <v>569</v>
-      </c>
       <c r="EW32" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="EX32" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="1:152">
       <c r="T33" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="U33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="V33" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="Z33" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="AA33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="AB33" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="AR33" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="AS33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="AT33" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="AX33" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="AY33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="AZ33" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="BP33" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="BQ33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="BR33" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="BV33" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="BW33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="BX33" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="CN33" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="CO33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="CP33" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="CT33" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="CU33" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="CV33" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="34" spans="1:152">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="G34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="M34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="AE34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="AK34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="BC34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="BI34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="CA34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="CG34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="CY34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="DE34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="DK34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="DQ34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="DW34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="EC34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="EI34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="EO34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="EU34" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
     </row>
     <row r="35" spans="1:152">
       <c r="B35" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="H35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="N35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="AF35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="AL35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="BD35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="BJ35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="CB35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="CH35" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="CZ35" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="DF35" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="DL35" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="DR35" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="DX35" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="ED35" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="EJ35" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="EP35" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="EV35" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
     </row>
     <row r="36" spans="1:152">
       <c r="B36" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="N36" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="AL36" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="BJ36" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="CH36" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="CZ36" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="DF36" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="DL36" t="s">
+        <v>572</v>
+      </c>
+      <c r="DR36" t="s">
+        <v>581</v>
+      </c>
+      <c r="DX36" t="s">
         <v>582</v>
       </c>
-      <c r="DR36" t="s">
-        <v>591</v>
-      </c>
-      <c r="DX36" t="s">
-        <v>592</v>
-      </c>
       <c r="EJ36" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="EP36" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="EV36" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37" spans="1:152">
       <c r="B37" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="N37" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AL37" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="BJ37" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="CH37" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="CZ37" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="DL37" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="DR37" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="EP37" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="EV37" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="38" spans="1:152">
       <c r="B38" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="DL38" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
     </row>
     <row r="39" spans="1:152">
       <c r="B39" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
     <row r="40" spans="1:152">
       <c r="B40" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
     </row>
     <row r="41" spans="1:152">
       <c r="B41" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
